--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <x:si>
     <x:t>구분</x:t>
   </x:si>
@@ -40,40 +40,25 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 플레이어 구현
-1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 스테이지 맵 모델링
 2. 플레이어 / 몬스터 에셋 적용
 3. 플레이어 / 몬스터 애니메이션 적용
 4. 플레이어 / 몬스터 구현사항 프리팹화
 5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
 6. 밤하늘 Material 적용
-7. 탈출구 위치 알림용 경광등 구현
-7.1. 프로토 타입으로, 추후 수정 예정</x:t>
+7. 탈출구 위치 알림용 경광등 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
   </x:si>
   <x:si>
     <x:t>2022.08.20(토)</x:t>
@@ -96,14 +81,30 @@
     <x:t>2022.08.24(수)</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 플레이어 구현
-1.1. 완료
-1.2. 완료
-1.3. 완료
-1.4. 완료</x:t>
+    <x:t>1. 몬스터 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
   </x:si>
   <x:si>
     <x:t>1. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
   </x:si>
   <x:si>
     <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
@@ -111,6 +112,15 @@
 3. 체력에 따른 영상효과(흑백처리)</x:t>
   </x:si>
   <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
     <x:t>2022.08.16(화)</x:t>
   </x:si>
   <x:si>
@@ -132,6 +142,15 @@
   </x:si>
   <x:si>
     <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 완료
+5. 완료
+6. 완료
+7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -873,7 +892,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="B6:D29"/>
+  <x:dimension ref="B6:D32"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="2" max="2" width="24.5" customWidth="1"/>
@@ -886,7 +905,7 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
         <x:v>1</x:v>
@@ -895,58 +914,58 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="2:4" ht="81.849999999999994">
+    <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+    </x:row>
+    <x:row r="8" spans="2:4" ht="81.849999999999994">
+      <x:c r="B8" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="2:4" ht="114.59999999999999">
+      <x:c r="B9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="2:4" ht="98.25">
-      <x:c r="B8" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="2:4" ht="131">
-      <x:c r="B9" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:3" ht="98.25">
       <x:c r="B10" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:3">
       <x:c r="B11" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:3" ht="49.149999999999999">
       <x:c r="B12" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>18</x:v>
@@ -954,54 +973,106 @@
     </x:row>
     <x:row r="13" spans="2:3">
       <x:c r="B13" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:3">
       <x:c r="B14" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:2">
       <x:c r="B15" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:2">
       <x:c r="B16" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2">
       <x:c r="B17" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="2:2">
+      <x:c r="B20" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="2:3" ht="49.149999999999999">
+      <x:c r="B21" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="2:3">
+      <x:c r="B22" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C22" s="1"/>
+    </x:row>
+    <x:row r="23" spans="2:3">
+      <x:c r="B23" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C23" s="1"/>
+    </x:row>
+    <x:row r="24" spans="2:3" ht="147.34999999999999">
+      <x:c r="B24" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="2:2">
+      <x:c r="B25" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="2:2">
+      <x:c r="B26" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="2:2">
       <x:c r="B27" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="2:3" ht="49.149999999999999">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="2:2">
       <x:c r="B28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="2:3" ht="147.34999999999999">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="2:2">
       <x:c r="B29" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="2:2">
+      <x:c r="B30" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="2:2">
+      <x:c r="B31" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="2:2">
+      <x:c r="B32" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -19,15 +19,67 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 스테이지 맵 모델링
+2. 플레이어 / 몬스터 에셋 적용
+3. 플레이어 / 몬스터 애니메이션 적용
+4. 플레이어 / 몬스터 구현사항 프리팹화
+5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
+6. 밤하늘 Material 적용
+7. 탈출구 위치 알림용 경광등 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 리팩토링
+2. 퍼즐 요소 추가(미션)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -40,110 +92,6 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 스테이지 맵 모델링
-2. 플레이어 / 몬스터 에셋 적용
-3. 플레이어 / 몬스터 애니메이션 적용
-4. 플레이어 / 몬스터 구현사항 프리팹화
-5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
-6. 밤하늘 Material 적용
-7. 탈출구 위치 알림용 경광등 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 완료
 2. 완료
 3. 완료
@@ -151,6 +99,70 @@
 5. 완료
 6. 완료
 7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 완료
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -218,7 +230,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="4">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -895,188 +910,194 @@
   <x:dimension ref="B6:D32"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.399999999999999"/>
   <x:cols>
-    <x:col min="2" max="2" width="24.5" customWidth="1"/>
-    <x:col min="3" max="3" width="80.125" customWidth="1"/>
-    <x:col min="4" max="4" width="90.625" customWidth="1"/>
-    <x:col min="6" max="6" width="26.75" customWidth="1"/>
-    <x:col min="7" max="7" width="67.625" customWidth="1"/>
-    <x:col min="8" max="8" width="58.25" customWidth="1"/>
+    <x:col min="2" max="2" width="24.5" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="80.125" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="90.625" style="1" customWidth="1"/>
+    <x:col min="6" max="6" width="26.75" style="1" customWidth="1"/>
+    <x:col min="7" max="7" width="67.625" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="58.25" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="6" spans="2:4">
-      <x:c r="B6" t="s">
+      <x:c r="B6" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D6" s="3" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C6" s="2" t="s">
+    </x:row>
+    <x:row r="7" spans="2:4" ht="131">
+      <x:c r="B7" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="2:4" ht="81.849999999999994">
+      <x:c r="B8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D6" s="2" t="s">
+      <x:c r="D8" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="2:4" ht="114.59999999999999">
+      <x:c r="B9" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="s">
         <x:v>2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" spans="2:4" ht="131">
-      <x:c r="B7" t="s">
+      <x:c r="D9" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="2:4" ht="98.25">
+      <x:c r="B10" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="2:3">
+      <x:c r="B11" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="2:3" ht="49.149999999999999">
+      <x:c r="B12" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="2:3" ht="32.75">
+      <x:c r="B13" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="2:3">
+      <x:c r="B14" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="2:3">
+      <x:c r="B15" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C15" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="2:2">
+      <x:c r="B16" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="s">
+    </x:row>
+    <x:row r="17" spans="2:2">
+      <x:c r="B17" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="2:2">
+      <x:c r="B20" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="2:3" ht="49.149999999999999">
+      <x:c r="B21" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C21" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="2:3">
+      <x:c r="B22" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C22" s="2"/>
+    </x:row>
+    <x:row r="23" spans="2:3">
+      <x:c r="B23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C23" s="2"/>
+    </x:row>
+    <x:row r="24" spans="2:3" ht="147.34999999999999">
+      <x:c r="B24" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C24" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="2:2">
+      <x:c r="B25" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="2:2">
+      <x:c r="B26" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="2:2">
+      <x:c r="B27" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="2:2">
+      <x:c r="B28" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="2:2">
+      <x:c r="B29" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+    </x:row>
+    <x:row r="30" spans="2:2">
+      <x:c r="B30" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="2:4" ht="81.849999999999994">
-      <x:c r="B8" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="2:4" ht="114.59999999999999">
-      <x:c r="B9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="2:3" ht="98.25">
-      <x:c r="B10" t="s">
+    <x:row r="31" spans="2:2">
+      <x:c r="B31" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="2:2">
+      <x:c r="B32" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="2:3">
-      <x:c r="B11" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="2:3" ht="49.149999999999999">
-      <x:c r="B12" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="2:3">
-      <x:c r="B13" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="2:3">
-      <x:c r="B14" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="2:2">
-      <x:c r="B15" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="2:2">
-      <x:c r="B16" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="2:2">
-      <x:c r="B17" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="2:2">
-      <x:c r="B20" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="2:3" ht="49.149999999999999">
-      <x:c r="B21" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C21" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="2:3">
-      <x:c r="B22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C22" s="1"/>
-    </x:row>
-    <x:row r="23" spans="2:3">
-      <x:c r="B23" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C23" s="1"/>
-    </x:row>
-    <x:row r="24" spans="2:3" ht="147.34999999999999">
-      <x:c r="B24" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="2:2">
-      <x:c r="B25" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="2:2">
-      <x:c r="B26" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="2:2">
-      <x:c r="B27" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="2:2">
-      <x:c r="B28" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="2:2">
-      <x:c r="B29" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="2:2">
-      <x:c r="B30" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="2:2">
-      <x:c r="B31" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="2:2">
-      <x:c r="B32" t="s">
-        <x:v>8</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51180553436279297" footer="0.51180553436279297"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51166665554046631" footer="0.51166665554046631"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -21,27 +21,21 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 스테이지 맵 모델링
-2. 플레이어 / 몬스터 에셋 적용
-3. 플레이어 / 몬스터 애니메이션 적용
-4. 플레이어 / 몬스터 구현사항 프리팹화
-5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
-6. 밤하늘 Material 적용
-7. 탈출구 위치 알림용 경광등 구현</x:t>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
   </x:si>
   <x:si>
     <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
@@ -51,35 +45,6 @@
   1.4. 완료
   1.5. 완료
   1.6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 리팩토링
-2. 퍼즐 요소 추가(미션)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -92,6 +57,102 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 리팩토링
+2. 퍼즐 요소 추가(미션)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 완료
+6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 스테이지 맵 모델링
+2. 플레이어 / 몬스터 에셋 적용
+3. 플레이어 / 몬스터 애니메이션 적용
+4. 플레이어 / 몬스터 구현사항 프리팹화
+5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
+6. 밤하늘 Material 적용
+7. 탈출구 위치 알림용 경광등 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 완료
 2. 완료
 3. 완료
@@ -99,67 +160,6 @@
 5. 완료
 6. 완료
 7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 완료
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
   </x:si>
   <x:si>
     <x:t>일자별 이슈</x:t>
@@ -230,7 +230,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -910,194 +913,194 @@
   <x:dimension ref="B6:D32"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.399999999999999"/>
   <x:cols>
-    <x:col min="2" max="2" width="24.5" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="80.125" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="90.625" style="1" customWidth="1"/>
-    <x:col min="6" max="6" width="26.75" style="1" customWidth="1"/>
-    <x:col min="7" max="7" width="67.625" style="1" customWidth="1"/>
-    <x:col min="8" max="8" width="58.25" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="24.5" style="2" customWidth="1"/>
+    <x:col min="3" max="3" width="80.125" style="2" customWidth="1"/>
+    <x:col min="4" max="4" width="90.625" style="2" customWidth="1"/>
+    <x:col min="6" max="6" width="26.75" style="2" customWidth="1"/>
+    <x:col min="7" max="7" width="67.625" style="2" customWidth="1"/>
+    <x:col min="8" max="8" width="58.25" style="2" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="6" spans="2:4">
-      <x:c r="B6" s="1" t="s">
+      <x:c r="B6" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="2:4" ht="131">
+      <x:c r="B7" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="2:4" ht="81.849999999999994">
+      <x:c r="B8" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="2:4" ht="114.59999999999999">
+      <x:c r="B9" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="2:4" ht="98.25">
+      <x:c r="B10" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D6" s="3" t="s">
+    </x:row>
+    <x:row r="11" spans="2:3">
+      <x:c r="B11" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="2:3" ht="49.149999999999999">
+      <x:c r="B12" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="2:3" ht="32.75">
+      <x:c r="B13" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7" spans="2:4" ht="131">
-      <x:c r="B7" s="1" t="s">
+      <x:c r="C13" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="2:3">
+      <x:c r="B14" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C7" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="s">
+    </x:row>
+    <x:row r="15" spans="2:3">
+      <x:c r="B15" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="2:2">
+      <x:c r="B16" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="2:2">
+      <x:c r="B17" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="2:2">
+      <x:c r="B20" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="2:3" ht="49.149999999999999">
+      <x:c r="B21" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C21" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="2:3">
+      <x:c r="B22" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C22" s="3"/>
+    </x:row>
+    <x:row r="23" spans="2:3">
+      <x:c r="B23" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C23" s="3"/>
+    </x:row>
+    <x:row r="24" spans="2:3" ht="147.34999999999999">
+      <x:c r="B24" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C24" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="2:4" ht="81.849999999999994">
-      <x:c r="B8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="2:4" ht="114.59999999999999">
-      <x:c r="B9" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C9" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="2:4" ht="98.25">
-      <x:c r="B10" s="1" t="s">
+    <x:row r="25" spans="2:2">
+      <x:c r="B25" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="2:2">
+      <x:c r="B26" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="2:2">
+      <x:c r="B27" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="2:2">
+      <x:c r="B28" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="2:2">
+      <x:c r="B29" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="2:2">
+      <x:c r="B30" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="2:2">
+      <x:c r="B31" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C10" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="2:3">
-      <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="2:3" ht="49.149999999999999">
-      <x:c r="B12" s="1" t="s">
+    </x:row>
+    <x:row r="32" spans="2:2">
+      <x:c r="B32" s="2" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C12" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="2:3" ht="32.75">
-      <x:c r="B13" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C13" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="2:3">
-      <x:c r="B14" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="2:3">
-      <x:c r="B15" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C15" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="2:2">
-      <x:c r="B16" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="2:2">
-      <x:c r="B17" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="2:2">
-      <x:c r="B20" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="2:3" ht="49.149999999999999">
-      <x:c r="B21" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C21" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="2:3">
-      <x:c r="B22" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C22" s="2"/>
-    </x:row>
-    <x:row r="23" spans="2:3">
-      <x:c r="B23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C23" s="2"/>
-    </x:row>
-    <x:row r="24" spans="2:3" ht="147.34999999999999">
-      <x:c r="B24" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C24" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="2:2">
-      <x:c r="B25" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="2:2">
-      <x:c r="B26" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="2:2">
-      <x:c r="B27" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="2:2">
-      <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="2:2">
-      <x:c r="B29" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="2:2">
-      <x:c r="B30" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="2:2">
-      <x:c r="B31" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="2:2">
-      <x:c r="B32" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51166665554046631" footer="0.51166665554046631"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51152777671813965" footer="0.51152777671813965"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -21,6 +21,27 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
   1.1. 1인칭 시점 카메라 세팅
   1.2. 마우스로 시점/회전 구현
@@ -30,21 +51,11 @@
   1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+    <x:t>1. 몬스터 구현
   1.1. 완료
   1.2. 완료
   1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
+  1.4. 완료</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -57,37 +68,14 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
 2. 탈출구 조건 만족시 게이트 오픈 구현
 3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 리팩토링
-2. 퍼즐 요소 추가(미션)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
   </x:si>
   <x:si>
     <x:t>1. 몬스터 구현
@@ -97,12 +85,32 @@
   1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
   </x:si>
   <x:si>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 리팩토링
+2. 퍼즐 요소 추가(미션)</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 완료
 2. 완료
 3. 완료
-4. 맵 내 건물 / 미션장소 (구조물)설치
+4. 미완. 명일로 연장
 5. 완료
 6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 완료
+5. 완료
+6. 완료
+7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
   </x:si>
   <x:si>
     <x:t>1. 스테이지 맵 모델링
@@ -114,55 +122,49 @@
 7. 탈출구 위치 알림용 경광등 구현</x:t>
   </x:si>
   <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
     <x:t>2022.08.24(수)</x:t>
   </x:si>
   <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
+    <x:t>2022.08.22(월)</x:t>
   </x:si>
   <x:si>
     <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 완료
-5. 완료
-6. 완료
-7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -923,21 +925,21 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
         <x:v>2</x:v>
@@ -945,64 +947,64 @@
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="2:3">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="2:3" ht="32.75">
       <x:c r="B11" s="2" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:3" ht="49.149999999999999">
       <x:c r="B12" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="2:3" ht="32.75">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="2:3" ht="49.149999999999999">
       <x:c r="B13" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:3">
       <x:c r="B14" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>23</x:v>
@@ -1010,7 +1012,7 @@
     </x:row>
     <x:row r="15" spans="2:3">
       <x:c r="B15" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>23</x:v>
@@ -1018,7 +1020,7 @@
     </x:row>
     <x:row r="16" spans="2:2">
       <x:c r="B16" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2">
@@ -1028,40 +1030,40 @@
     </x:row>
     <x:row r="20" spans="2:2">
       <x:c r="B20" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:3" ht="49.149999999999999">
       <x:c r="B21" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="2:3">
       <x:c r="B22" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="3"/>
     </x:row>
     <x:row r="23" spans="2:3">
       <x:c r="B23" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="3"/>
     </x:row>
     <x:row r="24" spans="2:3" ht="147.34999999999999">
       <x:c r="B24" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="2:2">
       <x:c r="B25" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="2:2">
@@ -1071,27 +1073,27 @@
     </x:row>
     <x:row r="27" spans="2:2">
       <x:c r="B27" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="2:2">
       <x:c r="B28" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="2:2">
       <x:c r="B29" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="2:2">
       <x:c r="B30" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="2:2">
       <x:c r="B31" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="2:2">
@@ -1100,7 +1102,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51152777671813965" footer="0.51152777671813965"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -21,27 +21,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
   <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
   1.1. 1인칭 시점 카메라 세팅
   1.2. 마우스로 시점/회전 구현
@@ -56,6 +35,31 @@
   1.2. 완료
   1.3. 완료
   1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 완료
+5. 완료
+6. 완료
+7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -73,21 +77,60 @@
 3. 기타</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-1. 리팩토링
-2. 퍼즐 요소 추가(미션)</x:t>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
@@ -98,19 +141,21 @@
 6. 완료</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 완료
-5. 완료
-6. 완료
-7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 리팩토링
+2. 퍼즐 요소 추가(미션)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
   </x:si>
   <x:si>
     <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
   </x:si>
   <x:si>
     <x:t>1. 스테이지 맵 모델링
@@ -120,51 +165,6 @@
 5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
 6. 밤하늘 Material 적용
 7. 탈출구 위치 알림용 경광등 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -925,65 +925,65 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="C10" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="3" t="s">
-        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:3" ht="32.75">
       <x:c r="B11" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:3" ht="49.149999999999999">
@@ -991,84 +991,84 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:3" ht="49.149999999999999">
       <x:c r="B13" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:3">
       <x:c r="B14" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:3">
       <x:c r="B15" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:2">
       <x:c r="B16" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2">
       <x:c r="B17" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="2:2">
       <x:c r="B20" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:3" ht="49.149999999999999">
       <x:c r="B21" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="2:3">
       <x:c r="B22" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C22" s="3"/>
     </x:row>
     <x:row r="23" spans="2:3">
       <x:c r="B23" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C23" s="3"/>
     </x:row>
     <x:row r="24" spans="2:3" ht="147.34999999999999">
       <x:c r="B24" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="2:2">
       <x:c r="B25" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="2:2">
       <x:c r="B26" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="2:2">
@@ -1078,27 +1078,27 @@
     </x:row>
     <x:row r="28" spans="2:2">
       <x:c r="B28" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="2:2">
       <x:c r="B29" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="2:2">
       <x:c r="B30" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="2:2">
       <x:c r="B31" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="2:2">
       <x:c r="B32" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="30">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <x:si>
     <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
   1.1. 1인칭 시점 카메라 세팅
@@ -30,36 +30,127 @@
   1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
   </x:si>
   <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 스테이지 맵 모델링
+2. 플레이어 / 몬스터 에셋 적용
+3. 플레이어 / 몬스터 애니메이션 적용
+4. 플레이어 / 몬스터 구현사항 프리팹화
+5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
+6. 밤하늘 Material 적용
+7. 탈출구 위치 알림용 경광등 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 미완
+2, 완료
+3. 완료
++  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
++  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완, 명일로 연장
++  전일 4번 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>**지도교수님 피드백 후 마저 진행
+2. 퍼즐 요소 추가(미션)
++ UI 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 미완. 명일로 연장
+5. 완료
+6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 몬스터 구현
   1.1. 완료
   1.2. 완료
   1.3. 완료
   1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 완료
-5. 완료
-6. 완료
-7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -72,99 +163,20 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
 2. 완료
 3. 완료
-4. 미완. 명일로 연장
+4. 완료
 5. 완료
-6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-1. 리팩토링
-2. 퍼즐 요소 추가(미션)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 스테이지 맵 모델링
-2. 플레이어 / 몬스터 에셋 적용
-3. 플레이어 / 몬스터 애니메이션 적용
-4. 플레이어 / 몬스터 구현사항 프리팹화
-5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
-6. 밤하늘 Material 적용
-7. 탈출구 위치 알림용 경광등 구현</x:t>
+6. 완료
+7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -925,180 +937,186 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="2:4" ht="49.149999999999999">
+      <x:c r="B11" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C10" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="2:3" ht="32.75">
-      <x:c r="B11" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C11" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="2:3" ht="49.149999999999999">
+    </x:row>
+    <x:row r="12" spans="2:4" ht="81.849999999999994">
       <x:c r="B12" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:3" ht="49.149999999999999">
       <x:c r="B13" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:3">
       <x:c r="B14" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:3">
       <x:c r="B15" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:2">
       <x:c r="B16" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2">
       <x:c r="B17" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="2:2">
       <x:c r="B20" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:3" ht="49.149999999999999">
       <x:c r="B21" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="2:3">
       <x:c r="B22" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="3"/>
     </x:row>
     <x:row r="23" spans="2:3">
       <x:c r="B23" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C23" s="3"/>
     </x:row>
     <x:row r="24" spans="2:3" ht="147.34999999999999">
       <x:c r="B24" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="2:2">
       <x:c r="B25" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="2:2">
       <x:c r="B26" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="2:2">
       <x:c r="B27" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="2:2">
       <x:c r="B28" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="2:2">
       <x:c r="B29" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="2:2">
       <x:c r="B30" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="2:2">
       <x:c r="B31" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="2:2">
       <x:c r="B32" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -21,78 +21,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 스테이지 맵 모델링
-2. 플레이어 / 몬스터 에셋 적용
-3. 플레이어 / 몬스터 애니메이션 적용
-4. 플레이어 / 몬스터 구현사항 프리팹화
-5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
-6. 밤하늘 Material 적용
-7. 탈출구 위치 알림용 경광등 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 미완
-2, 완료
-3. 완료
-+  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
-+  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 아이템 효과 구현
+2. 퍼즐 요소 추가(미션)
++ UI 구현</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
@@ -108,49 +40,62 @@
 6. 사운드 추가</x:t>
   </x:si>
   <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-2. 퍼즐 요소 추가(미션)
-+ UI 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
+    <x:t>일자별 이슈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 미완
+2, 완료
 3. 완료
-4. 미완. 명일로 연장
-5. 완료
-6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
++  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
++  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
   </x:si>
   <x:si>
     <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
 2. 탈출구 조건 만족시 게이트 오픈 구현
 3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -164,10 +109,26 @@
   </x:si>
   <x:si>
     <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
@@ -177,6 +138,46 @@
 5. 완료
 6. 완료
 7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 스테이지 맵 모델링
+2. 플레이어 / 몬스터 에셋 적용
+3. 플레이어 / 몬스터 애니메이션 적용
+4. 플레이어 / 몬스터 구현사항 프리팹화
+5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
+6. 밤하늘 Material 적용
+7. 탈출구 위치 알림용 경광등 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 미완. 명일로 연장
+5. 완료
+6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -937,186 +938,186 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:4" ht="49.149999999999999">
       <x:c r="B11" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:4" ht="81.849999999999994">
       <x:c r="B12" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="2:3" ht="49.149999999999999">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="2:3" ht="65.5">
       <x:c r="B13" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:3">
       <x:c r="B14" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:3">
       <x:c r="B15" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:2">
       <x:c r="B16" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2">
       <x:c r="B17" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="2:2">
       <x:c r="B20" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:3" ht="49.149999999999999">
       <x:c r="B21" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="2:3">
       <x:c r="B22" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C22" s="3"/>
     </x:row>
     <x:row r="23" spans="2:3">
       <x:c r="B23" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="3"/>
     </x:row>
     <x:row r="24" spans="2:3" ht="147.34999999999999">
       <x:c r="B24" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C24" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="2:2">
       <x:c r="B25" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="2:2">
       <x:c r="B26" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="2:2">
       <x:c r="B27" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="2:2">
       <x:c r="B28" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="2:2">
       <x:c r="B29" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="2:2">
       <x:c r="B30" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="2:2">
       <x:c r="B31" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="2:2">
       <x:c r="B32" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -19,17 +19,103 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
-  <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-1. 아이템 효과 구현
-2. 퍼즐 요소 추가(미션)
-+ UI 구현</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 미완. 명일로 연장
+5. 완료
+6. 완료</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
 2. 미완, 명일로 연장
 +  전일 4번 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 인게임 UI 마무리 - 체력바, 배터리 게이지 변경예정
+2. HeartRate UI 추가
+3. 미션진행 UI 추가(게이지
+4. 게임오버 UI 및 리셋기능 구현
+5. 메인타이틀 UI 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
   </x:si>
   <x:si>
     <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
@@ -40,57 +126,48 @@
 6. 사운드 추가</x:t>
   </x:si>
   <x:si>
-    <x:t>일자별 이슈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 퍼즐 요소 추가(미션)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 미완
 2, 완료
 3. 완료
 +  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
 +  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 스테이지 맵 모델링
+2. 플레이어 / 몬스터 에셋 적용
+3. 플레이어 / 몬스터 애니메이션 적용
+4. 플레이어 / 몬스터 구현사항 프리팹화
+5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
+6. 밤하늘 Material 적용
+7. 탈출구 위치 알림용 경광등 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완
+3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 아이템 효과 구현
+2. 퍼즐 요소 추가(미션)
++ UI 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 메인타이틀 UI 구현
+2. 테스트 및 게임 밸런스 조정
+3. 코드 리팩토링</x:t>
   </x:si>
   <x:si>
     <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
@@ -108,29 +185,6 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 완료
 2. 완료
 3. 완료
@@ -140,44 +194,14 @@
 7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 스테이지 맵 모델링
-2. 플레이어 / 몬스터 에셋 적용
-3. 플레이어 / 몬스터 애니메이션 적용
-4. 플레이어 / 몬스터 구현사항 프리팹화
-5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
-6. 밤하늘 Material 적용
-7. 탈출구 위치 알림용 경광등 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 미완. 명일로 연장
-5. 완료
-6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
+    <x:t>기타
+1. 2022.08.18 발생했던 Git 오류 지속.
+  1.1. 지도교수께서 직접 설정해 주셨으나 문제 지속
+  1.2. 더 이상 시간을 지체할 수 없어 신규 레포지토리 개설토록 함
+기획
+1. UI 및 게임 내 시스템 구현일정에 딜레이가 생겨 퍼즐요소 추가여부가 불가피함
+  1.1. 퍼즐요소는 배제 후 최대한 게임 시스템 구성에 집중
+  1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -245,10 +269,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -928,196 +949,202 @@
   <x:dimension ref="B6:D32"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.399999999999999"/>
   <x:cols>
-    <x:col min="2" max="2" width="24.5" style="2" customWidth="1"/>
-    <x:col min="3" max="3" width="80.125" style="2" customWidth="1"/>
-    <x:col min="4" max="4" width="90.625" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="26.75" style="2" customWidth="1"/>
-    <x:col min="7" max="7" width="67.625" style="2" customWidth="1"/>
-    <x:col min="8" max="8" width="58.25" style="2" customWidth="1"/>
+    <x:col min="2" max="2" width="24.5" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="80.125" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="90.625" style="1" customWidth="1"/>
+    <x:col min="6" max="6" width="26.75" style="1" customWidth="1"/>
+    <x:col min="7" max="7" width="67.625" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="58.25" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="6" spans="2:4">
-      <x:c r="B6" s="2" t="s">
+      <x:c r="B6" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="2:4" ht="131">
+      <x:c r="B7" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="2:4" ht="81.849999999999994">
+      <x:c r="B8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="2:4" ht="114.59999999999999">
+      <x:c r="B9" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="2:4" ht="98.25">
+      <x:c r="B10" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="2:4" ht="49.149999999999999">
+      <x:c r="B11" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="2:4" ht="81.849999999999994">
+      <x:c r="B12" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C12" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="2:4" ht="65.5">
+      <x:c r="B13" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="2:3" ht="81.849999999999994">
+      <x:c r="B14" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="2:3" ht="49.149999999999999">
+      <x:c r="B15" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C15" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="2:2">
+      <x:c r="B16" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="2:2">
+      <x:c r="B17" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="2:2">
+      <x:c r="B20" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C6" s="4" t="s">
+    </x:row>
+    <x:row r="21" spans="2:3" ht="49.149999999999999">
+      <x:c r="B21" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C21" s="2" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D6" s="4" t="s">
-        <x:v>31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="2:4" ht="131">
-      <x:c r="B7" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D7" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="2:4" ht="81.849999999999994">
-      <x:c r="B8" s="2" t="s">
+    </x:row>
+    <x:row r="22" spans="2:3">
+      <x:c r="B22" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C22" s="2"/>
+    </x:row>
+    <x:row r="23" spans="2:3">
+      <x:c r="B23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="3" t="s">
+      <x:c r="C23" s="2"/>
+    </x:row>
+    <x:row r="24" spans="2:3" ht="147.34999999999999">
+      <x:c r="B24" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C24" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="2:2">
+      <x:c r="B25" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="2:4" ht="114.59999999999999">
-      <x:c r="B9" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D9" s="3" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="2:4" ht="98.25">
-      <x:c r="B10" s="2" t="s">
+    <x:row r="26" spans="2:2">
+      <x:c r="B26" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="2:2">
+      <x:c r="B27" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="2:3" ht="147.34999999999999">
+      <x:c r="B28" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C28" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="2:2">
+      <x:c r="B29" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C10" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="3" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="2:4" ht="49.149999999999999">
-      <x:c r="B11" s="2" t="s">
+    </x:row>
+    <x:row r="30" spans="2:2">
+      <x:c r="B30" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="2:2">
+      <x:c r="B31" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C11" s="3" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D11" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="2:4" ht="81.849999999999994">
-      <x:c r="B12" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="3" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D12" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="2:3" ht="65.5">
-      <x:c r="B13" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="2:3">
-      <x:c r="B14" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="2:3">
-      <x:c r="B15" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="2:2">
-      <x:c r="B16" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="2:2">
-      <x:c r="B17" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="2:2">
-      <x:c r="B20" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="2:3" ht="49.149999999999999">
-      <x:c r="B21" s="2" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C21" s="3" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="2:3">
-      <x:c r="B22" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C22" s="3"/>
-    </x:row>
-    <x:row r="23" spans="2:3">
-      <x:c r="B23" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C23" s="3"/>
-    </x:row>
-    <x:row r="24" spans="2:3" ht="147.34999999999999">
-      <x:c r="B24" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C24" s="3" t="s">
+    </x:row>
+    <x:row r="32" spans="2:2">
+      <x:c r="B32" s="1" t="s">
         <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="2:2">
-      <x:c r="B25" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="2:2">
-      <x:c r="B26" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="2:2">
-      <x:c r="B27" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="2:2">
-      <x:c r="B28" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="2:2">
-      <x:c r="B29" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="2:2">
-      <x:c r="B30" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="2:2">
-      <x:c r="B31" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="2:2">
-      <x:c r="B32" s="2" t="s">
-        <x:v>10</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -19,28 +19,44 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 미완. 명일로 연장
-5. 완료
-6. 완료</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
 2. 미완, 명일로 연장
 +  전일 4번 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
   </x:si>
   <x:si>
     <x:t>1. 몬스터 구현
@@ -50,6 +66,24 @@
   1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
   </x:si>
   <x:si>
+    <x:t>기타
+1. 2022.08.18 발생했던 Git 오류 지속.
+  1.1. 지도교수께서 직접 설정해 주셨으나 문제 지속
+  1.2. 더 이상 시간을 지체할 수 없어 신규 레포지토리 개설토록 함
+기획
+1. UI 및 게임 내 시스템 구현일정에 딜레이가 생겨 퍼즐요소 추가여부가 불가피함
+  1.1. 퍼즐요소는 배제 후 최대한 게임 시스템 구성에 집중
+  1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 인게임 UI 마무리 - 체력바, 배터리 게이지 변경예정
 2. HeartRate UI 추가
 3. 미션진행 UI 추가(게이지
@@ -57,11 +91,23 @@
 5. 메인타이틀 UI 설계</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
   </x:si>
   <x:si>
     <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
@@ -73,40 +119,58 @@
   1.6. 완료</x:t>
   </x:si>
   <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타
+1.신규 레포지토리 개설, 기획안 하단 링크 첨부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 미완
+2, 완료
+3. 완료
++  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
++  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 아이템 효과 구현
+2. 퍼즐 요소 추가(미션)
++ UI 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 완료
+5. 완료
+6. 완료
+7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 스테이지 맵 모델링
+2. 플레이어 / 몬스터 에셋 적용
+3. 플레이어 / 몬스터 애니메이션 적용
+4. 플레이어 / 몬스터 구현사항 프리팹화
+5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
+6. 밤하늘 Material 적용
+7. 탈출구 위치 알림용 경광등 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완
+3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
   </x:si>
   <x:si>
     <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
@@ -116,63 +180,6 @@
   1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
   1.5 뛰기/걷기 구현
   1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 미완
-2, 완료
-3. 완료
-+  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
-+  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 스테이지 맵 모델링
-2. 플레이어 / 몬스터 에셋 적용
-3. 플레이어 / 몬스터 애니메이션 적용
-4. 플레이어 / 몬스터 구현사항 프리팹화
-5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
-6. 밤하늘 Material 적용
-7. 탈출구 위치 알림용 경광등 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 미완
-3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-1. 아이템 효과 구현
-2. 퍼즐 요소 추가(미션)
-+ UI 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 메인타이틀 UI 구현
-2. 테스트 및 게임 밸런스 조정
-3. 코드 리팩토링</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -185,23 +192,23 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
+    <x:t>1. 메인타이틀 UI 구현
+2. 테스트 및 게임 밸런스 조정
+3. 코드 리팩토링</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 완료
 2. 완료
 3. 완료
-4. 완료
+4. 미완. 명일로 연장
 5. 완료
-6. 완료
-7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기타
-1. 2022.08.18 발생했던 Git 오류 지속.
-  1.1. 지도교수께서 직접 설정해 주셨으나 문제 지속
-  1.2. 더 이상 시간을 지체할 수 없어 신규 레포지토리 개설토록 함
-기획
-1. UI 및 게임 내 시스템 구현일정에 딜레이가 생겨 퍼즐요소 추가여부가 불가피함
-  1.1. 퍼즐요소는 배제 후 최대한 게임 시스템 구성에 집중
-  1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
+6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Git 레포지토리 신규 개설</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -959,76 +966,76 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:4" ht="49.149999999999999">
       <x:c r="B11" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:4" ht="81.849999999999994">
       <x:c r="B12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
         <x:v>24</x:v>
@@ -1036,69 +1043,72 @@
     </x:row>
     <x:row r="13" spans="2:4" ht="65.5">
       <x:c r="B13" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="2:3" ht="81.849999999999994">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="2:4" ht="81.849999999999994">
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:3" ht="49.149999999999999">
       <x:c r="B15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:2">
       <x:c r="B16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2">
       <x:c r="B17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="2:2">
       <x:c r="B20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:3" ht="49.149999999999999">
       <x:c r="B21" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C21" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="2:3">
       <x:c r="B22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C22" s="2"/>
     </x:row>
     <x:row r="23" spans="2:3">
       <x:c r="B23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C23" s="2"/>
     </x:row>
     <x:row r="24" spans="2:3" ht="147.34999999999999">
       <x:c r="B24" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C24" s="2" t="s">
         <x:v>32</x:v>
@@ -1106,45 +1116,48 @@
     </x:row>
     <x:row r="25" spans="2:2">
       <x:c r="B25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="2:2">
       <x:c r="B26" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="2:2">
       <x:c r="B27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="2:3" ht="147.34999999999999">
       <x:c r="B28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="2:2">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="2:3" ht="32.75">
       <x:c r="B29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="2" t="s">
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="2:2">
       <x:c r="B30" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="2:2">
       <x:c r="B31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="2:2">
       <x:c r="B32" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -21,49 +21,28 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 미완, 명일로 연장
-+  전일 4번 완료</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 몬스터 구현
   1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
   1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
   1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
   1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 진행중
+5. 진행중
++ 인게임 'Pause' UI 추가
++ Git 레포지토리 신규 개설
++ 아이템 '배터리' 추가 - 배터리 게이지 40 회복 아이템</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 인게임 UI 마무리 - 체력바, 배터리 게이지 변경예정
+2. HeartRate UI 추가
+3. 미션진행 UI 추가(게이지
+4. 게임오버 UI 및 리셋기능 구현
+5. 메인타이틀 UI 설계</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -76,38 +55,11 @@
   1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 인게임 UI 마무리 - 체력바, 배터리 게이지 변경예정
-2. HeartRate UI 추가
-3. 미션진행 UI 추가(게이지
-4. 게임오버 UI 및 리셋기능 구현
-5. 메인타이틀 UI 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
+    <x:t>1. 미완
+2, 완료
+3. 완료
++  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
++  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
   </x:si>
   <x:si>
     <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
@@ -119,67 +71,12 @@
   1.6. 완료</x:t>
   </x:si>
   <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기타
-1.신규 레포지토리 개설, 기획안 하단 링크 첨부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 미완
-2, 완료
-3. 완료
-+  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
-+  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-1. 아이템 효과 구현
-2. 퍼즐 요소 추가(미션)
-+ UI 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 완료
-5. 완료
-6. 완료
-7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 스테이지 맵 모델링
-2. 플레이어 / 몬스터 에셋 적용
-3. 플레이어 / 몬스터 애니메이션 적용
-4. 플레이어 / 몬스터 구현사항 프리팹화
-5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
-6. 밤하늘 Material 적용
-7. 탈출구 위치 알림용 경광등 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 미완
-3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -192,6 +89,72 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 스테이지 맵 모델링
+2. 플레이어 / 몬스터 에셋 적용
+3. 플레이어 / 몬스터 애니메이션 적용
+4. 플레이어 / 몬스터 구현사항 프리팹화
+5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
+6. 밤하늘 Material 적용
+7. 탈출구 위치 알림용 경광등 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 아이템 효과 구현
+2. 퍼즐 요소 추가(미션)
++ UI 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 완료
+5. 완료
+6. 완료
+7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 메인타이틀 UI 구현
 2. 테스트 및 게임 밸런스 조정
 3. 코드 리팩토링</x:t>
@@ -208,7 +171,51 @@
     <x:t>일자별 이슈</x:t>
   </x:si>
   <x:si>
-    <x:t>Git 레포지토리 신규 개설</x:t>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완
+3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타
+1.신규 레포지토리 개설, 기획안 하단 링크 첨부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완, 명일로 연장
++  전일 4번 완료</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -966,198 +973,198 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:4" ht="49.149999999999999">
       <x:c r="B11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:4" ht="81.849999999999994">
       <x:c r="B12" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:4" ht="65.5">
       <x:c r="B13" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="2:4" ht="147.34999999999999">
+      <x:c r="B14" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C13" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="2:4" ht="81.849999999999994">
-      <x:c r="B14" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>36</x:v>
+      <x:c r="D14" s="2" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:3" ht="49.149999999999999">
       <x:c r="B15" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:2">
       <x:c r="B16" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2">
       <x:c r="B17" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="2:2">
       <x:c r="B20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:3" ht="49.149999999999999">
       <x:c r="B21" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C21" s="2" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="C21" s="2" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="2:3">
       <x:c r="B22" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C22" s="2"/>
     </x:row>
     <x:row r="23" spans="2:3">
       <x:c r="B23" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C23" s="2"/>
     </x:row>
     <x:row r="24" spans="2:3" ht="147.34999999999999">
       <x:c r="B24" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C24" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="2:2">
       <x:c r="B25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="2:2">
       <x:c r="B26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="2:2">
       <x:c r="B27" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="2:3" ht="147.34999999999999">
       <x:c r="B28" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="2:3" ht="32.75">
       <x:c r="B29" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="2:2">
       <x:c r="B30" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="2:2">
       <x:c r="B31" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="2:2">
       <x:c r="B32" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -21,21 +21,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 진행중
-5. 진행중
-+ 인게임 'Pause' UI 추가
-+ Git 레포지토리 신규 개설
-+ 아이템 '배터리' 추가 - 배터리 게이지 40 회복 아이템</x:t>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
   </x:si>
   <x:si>
     <x:t>1. 인게임 UI 마무리 - 체력바, 배터리 게이지 변경예정
@@ -43,6 +35,16 @@
 3. 미션진행 UI 추가(게이지
 4. 게임오버 UI 및 리셋기능 구현
 5. 메인타이틀 UI 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 진행중
+5. 완료
++ 인게임 'Pause' UI 추가
++ Git 레포지토리 신규 개설
++ 아이템 '배터리' 추가 - 배터리 게이지 40 회복 아이템</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -55,11 +57,25 @@
   1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 미완
-2, 완료
-3. 완료
-+  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
-+  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타
+1.신규 레포지토리 개설, 기획안 하단 링크 첨부
+구현
+1. AI 좀비의 방향은 랜덤(Random.Range)로 구현.
+  1.1. 테스트 결과 간혹 대체적으로 한쪽 방향으로 좀비가 쏠리는 방향이 발생.
+  1.2. 아직은 더 효과적인 방법을 모르겠음.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
   </x:si>
   <x:si>
     <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
@@ -71,12 +87,49 @@
   1.6. 완료</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 미완
+2, 완료
+3. 완료
++  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
++  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 아이템 효과 구현
+2. 퍼즐 요소 추가(미션)
++ UI 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완
+3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 완료
+5. 완료
+6. 완료
+7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -89,14 +142,6 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 스테이지 맵 모델링
 2. 플레이어 / 몬스터 에셋 적용
 3. 플레이어 / 몬스터 애니메이션 적용
@@ -106,55 +151,6 @@
 7. 탈출구 위치 알림용 경광등 구현</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-1. 아이템 효과 구현
-2. 퍼즐 요소 추가(미션)
-+ UI 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 완료
-5. 완료
-6. 완료
-7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 메인타이틀 UI 구현
 2. 테스트 및 게임 밸런스 조정
 3. 코드 리팩토링</x:t>
@@ -168,54 +164,62 @@
 6. 완료</x:t>
   </x:si>
   <x:si>
-    <x:t>일자별 이슈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 미완
-3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기타
-1.신규 레포지토리 개설, 기획안 하단 링크 첨부</x:t>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
 2. 미완, 명일로 연장
 +  전일 4번 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -973,57 +977,57 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:4" ht="49.149999999999999">
@@ -1031,10 +1035,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:4" ht="81.849999999999994">
@@ -1042,88 +1046,88 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:4" ht="65.5">
       <x:c r="B13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:4" ht="147.34999999999999">
       <x:c r="B14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="s">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="2" t="s">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:3" ht="49.149999999999999">
       <x:c r="B15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:2">
       <x:c r="B16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2">
       <x:c r="B17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="2:2">
       <x:c r="B20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:3" ht="49.149999999999999">
       <x:c r="B21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C21" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="2:3">
       <x:c r="B22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="2"/>
     </x:row>
     <x:row r="23" spans="2:3">
       <x:c r="B23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="2"/>
     </x:row>
     <x:row r="24" spans="2:3" ht="147.34999999999999">
       <x:c r="B24" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C24" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="2:2">
       <x:c r="B25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="2:2">
@@ -1138,33 +1142,33 @@
     </x:row>
     <x:row r="28" spans="2:3" ht="147.34999999999999">
       <x:c r="B28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="2:3" ht="32.75">
+    <x:row r="29" spans="2:3" ht="114.59999999999999">
       <x:c r="B29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="2:2">
       <x:c r="B30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="2:2">
       <x:c r="B31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="2:2">
       <x:c r="B32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -19,22 +19,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 인게임 UI 마무리 - 체력바, 배터리 게이지 변경예정
-2. HeartRate UI 추가
-3. 미션진행 UI 추가(게이지
-4. 게임오버 UI 및 리셋기능 구현
-5. 메인타이틀 UI 설계</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+  <x:si>
+    <x:t>1. 버그픽스
+2. 코드 리팩토링
+3. 게임 밸런스 조정</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
@@ -47,6 +36,167 @@
 + 아이템 '배터리' 추가 - 배터리 게이지 40 회복 아이템</x:t>
   </x:si>
   <x:si>
+    <x:t>1. 인게임 UI 마무리 - 체력바, 배터리 게이지 변경예정
+2. HeartRate UI 추가
+3. 미션진행 UI 추가(게이지
+4. 게임오버 UI 및 리셋기능 구현
+5. 메인타이틀 UI 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타
+1.신규 레포지토리 개설, 기획안 하단 링크 첨부
+구현
+1. AI 좀비의 방향은 랜덤(Random.Range)로 구현.
+  1.1. 테스트 결과 간혹 대체적으로 한쪽 방향으로 좀비가 쏠리는 방향이 발생.
+  1.2. 아직은 더 효과적인 방법을 모르겠음.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 스테이지 맵 모델링
+2. 플레이어 / 몬스터 에셋 적용
+3. 플레이어 / 몬스터 애니메이션 적용
+4. 플레이어 / 몬스터 구현사항 프리팹화
+5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
+6. 밤하늘 Material 적용
+7. 탈출구 위치 알림용 경광등 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 진행중
+3. 미완
+++ 게임매니저/씬메니저 구현 및 씬 변경 구현 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 아이템 효과 구현
+2. 퍼즐 요소 추가(미션)
++ UI 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 미완
+2, 완료
+3. 완료
++  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
++  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구현
+1. 빌드 후 게임 실행시 특정 구간에서 화면 프리징 발생
+  1.1. 특정 위치를 벗어나면 다시 움직임, 게임은 계속 진행되며 화면만 멈춤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타
+1. 사용하려고 했던 구조물 에셋의 개별 파일당 용량 초과(100MB이내 제한)로 Git push 에러 발생
+  1.1. (오후)지도교수님께 문의 결과 Git lfs 설치 권장.
+    1.1.1. 용량 초과하는 파일에 대해 쪼개서 push하는 방식
+    1.1.2. 추후 다운로드 시 pull을 통해 받아야 온전한 파일로 다운받을 수 있음
+  1.2. 검색 후 적용하려 했으나, 실패.
+    1.2.1. 명일 다시 여쭤보고 처리할 예정.
+    1.2.2. 처리 완료시까지 Commit 불가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 메인타이틀 UI 구현
+2. 테스트 및 게임 밸런스 조정
+3. 코드 리팩토링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완
+3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
     <x:t>기타
 1. 2022.08.18 발생했던 Git 오류 지속.
   1.1. 지도교수께서 직접 설정해 주셨으나 문제 지속
@@ -57,70 +207,12 @@
   1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기타
-1.신규 레포지토리 개설, 기획안 하단 링크 첨부
-구현
-1. AI 좀비의 방향은 랜덤(Random.Range)로 구현.
-  1.1. 테스트 결과 간혹 대체적으로 한쪽 방향으로 좀비가 쏠리는 방향이 발생.
-  1.2. 아직은 더 효과적인 방법을 모르겠음.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 미완
-2, 완료
+    <x:t>1. 완료
+2. 완료
 3. 완료
-+  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
-+  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-1. 아이템 효과 구현
-2. 퍼즐 요소 추가(미션)
-+ UI 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 미완
-3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
+4. 미완. 명일로 연장
+5. 완료
+6. 완료</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
@@ -132,94 +224,18 @@
 7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
   </x:si>
   <x:si>
-    <x:t>기타
-1. 사용하려고 했던 구조물 에셋의 개별 파일당 용량 초과(100MB이내 제한)로 Git push 에러 발생
-  1.1. (오후)지도교수님께 문의 결과 Git lfs 설치 권장.
-    1.1.1. 용량 초과하는 파일에 대해 쪼개서 push하는 방식
-    1.1.2. 추후 다운로드 시 pull을 통해 받아야 온전한 파일로 다운받을 수 있음
-  1.2. 검색 후 적용하려 했으나, 실패.
-    1.2.1. 명일 다시 여쭤보고 처리할 예정.
-    1.2.2. 처리 완료시까지 Commit 불가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 스테이지 맵 모델링
-2. 플레이어 / 몬스터 에셋 적용
-3. 플레이어 / 몬스터 애니메이션 적용
-4. 플레이어 / 몬스터 구현사항 프리팹화
-5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
-6. 밤하늘 Material 적용
-7. 탈출구 위치 알림용 경광등 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 메인타이틀 UI 구현
-2. 테스트 및 게임 밸런스 조정
-3. 코드 리팩토링</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 미완. 명일로 연장
-5. 완료
-6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 완료
 2. 미완, 명일로 연장
 +  전일 4번 완료</x:t>
   </x:si>
   <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -977,198 +993,207 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:4" ht="49.149999999999999">
       <x:c r="B11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:4" ht="81.849999999999994">
       <x:c r="B12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:4" ht="65.5">
       <x:c r="B13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:4" ht="147.34999999999999">
       <x:c r="B14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D14" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="2:3" ht="49.149999999999999">
+    </x:row>
+    <x:row r="15" spans="2:4" ht="81.849999999999994">
       <x:c r="B15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="2:2">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="2:3" ht="49.149999999999999">
       <x:c r="B16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C16" s="2" t="s">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2">
       <x:c r="B17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="2:2">
       <x:c r="B20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:3" ht="49.149999999999999">
       <x:c r="B21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="2:3">
       <x:c r="B22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="2"/>
     </x:row>
     <x:row r="23" spans="2:3">
       <x:c r="B23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="2"/>
     </x:row>
     <x:row r="24" spans="2:3" ht="147.34999999999999">
       <x:c r="B24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C24" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="2:2">
       <x:c r="B25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="2:2">
       <x:c r="B26" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="2:2">
       <x:c r="B27" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="2:3" ht="147.34999999999999">
       <x:c r="B28" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="2:3" ht="114.59999999999999">
       <x:c r="B29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="2:2">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="2:3" ht="49.149999999999999">
       <x:c r="B30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C30" s="2" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="2:2">
       <x:c r="B31" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="2:2">
       <x:c r="B32" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -21,9 +21,37 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <x:si>
-    <x:t>1. 버그픽스
-2. 코드 리팩토링
-3. 게임 밸런스 조정</x:t>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
@@ -59,6 +87,11 @@
 6. 사운드 추가</x:t>
   </x:si>
   <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 스테이지 맵 모델링
 2. 플레이어 / 몬스터 에셋 적용
 3. 플레이어 / 몬스터 애니메이션 적용
@@ -68,6 +101,17 @@
 7. 탈출구 위치 알림용 경광등 구현</x:t>
   </x:si>
   <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 미완
+2, 완료
+3. 완료
++  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
++  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 몬스터 구현
   1.1. 완료
   1.2. 완료
@@ -78,91 +122,15 @@
     <x:t>1. 완료
 2. 진행중
 3. 미완
-++ 게임매니저/씬메니저 구현 및 씬 변경 구현 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-1. 아이템 효과 구현
-2. 퍼즐 요소 추가(미션)
-+ UI 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 미완
-2, 완료
-3. 완료
-+  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
-+  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구현
-1. 빌드 후 게임 실행시 특정 구간에서 화면 프리징 발생
-  1.1. 특정 위치를 벗어나면 다시 움직임, 게임은 계속 진행되며 화면만 멈춤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
+++ 게임매니저/씬메니저 구현 및 씬 변경 구현 완료
+Bug Fix:
+1. 케릭터, 좀비가 벽 뚫는 버그 수정
+2. 소환단계에서 좀비가 공중에 떠 있는 버그 수정
+3. 유니티 상에선 괜찮으나 빌드시 좀비 마주치면 화면만 프리징 되는 버그 수정
+Feat:
+1. UI추가(미션머신, 탈출구, Start Tip)
+  1.1. 미션머신 하단에 동그란 모양의 비콘이미지를 설치했으나, 지속적으로 깜빡거리는 증상 발생, 금일 새벽 ~ 명일 픽스 예정
+2. 메인타이틀 화면 단순 이미지로 전환</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -175,6 +143,49 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 아이템 효과 구현
+2. 퍼즐 요소 추가(미션)
++ UI 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 미완. 명일로 연장
+5. 완료
+6. 완료</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 메인타이틀 UI 구현
 2. 테스트 및 게임 밸런스 조정
 3. 코드 리팩토링</x:t>
@@ -185,16 +196,18 @@
 3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
+    <x:t>구현
+1. 빌드 후 게임 실행시 특정 구간에서 화면 프리징 발생
+  1.1. 특정 위치를 벗어나면 다시 움직임, 게임은 계속 진행되며 화면만 멈춤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 완료
+5. 완료
+6. 완료
+7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -207,35 +220,30 @@
   1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 미완. 명일로 연장
-5. 완료
-6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 완료
-5. 완료
-6. 완료
-7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 버그픽스
+2. 코드 리팩토링
+3. 게임 밸런스 조정</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
 2. 미완, 명일로 연장
 +  전일 4번 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -993,87 +1001,87 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:4" ht="49.149999999999999">
       <x:c r="B11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:4" ht="81.849999999999994">
       <x:c r="B12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:4" ht="65.5">
       <x:c r="B13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
         <x:v>32</x:v>
@@ -1081,42 +1089,42 @@
     </x:row>
     <x:row r="14" spans="2:4" ht="147.34999999999999">
       <x:c r="B14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="2:4" ht="81.849999999999994">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="2:4" ht="261.94999999999999">
       <x:c r="B15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:3" ht="49.149999999999999">
       <x:c r="B16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2">
       <x:c r="B17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="2:2">
       <x:c r="B20" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:3" ht="49.149999999999999">
@@ -1124,47 +1132,47 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="2:3">
       <x:c r="B22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C22" s="2"/>
     </x:row>
     <x:row r="23" spans="2:3">
       <x:c r="B23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="2"/>
     </x:row>
     <x:row r="24" spans="2:3" ht="147.34999999999999">
       <x:c r="B24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C24" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="2:2">
       <x:c r="B25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="2:2">
       <x:c r="B26" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="2:2">
       <x:c r="B27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="2:3" ht="147.34999999999999">
       <x:c r="B28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
         <x:v>35</x:v>
@@ -1172,28 +1180,28 @@
     </x:row>
     <x:row r="29" spans="2:3" ht="114.59999999999999">
       <x:c r="B29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="2:3" ht="49.149999999999999">
       <x:c r="B30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C30" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="2:2">
       <x:c r="B31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="2:2">
       <x:c r="B32" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -19,39 +19,55 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+  <x:si>
+    <x:t>1. 메인타이틀 UI 구현
+2. 테스트 및 게임 밸런스 조정
+3. 코드 리팩토링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완, 명일로 연장
++  전일 4번 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 버그픽스
+2. 코드 리팩토링
+3. 게임 밸런스 조정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 미완. 명일로 연장
+5. 완료
+6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 아이템 효과 구현
+2. 퍼즐 요소 추가(미션)
++ UI 구현</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
@@ -71,38 +87,14 @@
 5. 메인타이틀 UI 설계</x:t>
   </x:si>
   <x:si>
-    <x:t>기타
-1.신규 레포지토리 개설, 기획안 하단 링크 첨부
-구현
-1. AI 좀비의 방향은 랜덤(Random.Range)로 구현.
-  1.1. 테스트 결과 간혹 대체적으로 한쪽 방향으로 좀비가 쏠리는 방향이 발생.
-  1.2. 아직은 더 효과적인 방법을 모르겠음.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 스테이지 맵 모델링
-2. 플레이어 / 몬스터 에셋 적용
-3. 플레이어 / 몬스터 애니메이션 적용
-4. 플레이어 / 몬스터 구현사항 프리팹화
-5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
-6. 밤하늘 Material 적용
-7. 탈출구 위치 알림용 경광등 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완
+3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
   </x:si>
   <x:si>
     <x:t>1. 미완
@@ -113,17 +105,23 @@
   </x:si>
   <x:si>
     <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 진행중
-3. 미완
-++ 게임매니저/씬메니저 구현 및 씬 변경 구현 완료
-Bug Fix:
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타
+1. 2022.08.18 발생했던 Git 오류 지속.
+  1.1. 지도교수께서 직접 설정해 주셨으나 문제 지속
+  1.2. 더 이상 시간을 지체할 수 없어 신규 레포지토리 개설토록 함
+기획
+1. UI 및 게임 내 시스템 구현일정에 딜레이가 생겨 퍼즐요소 추가여부가 불가피함
+  1.1. 퍼즐요소는 배제 후 최대한 게임 시스템 구성에 집중
+  1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bug Fix:
 1. 케릭터, 좀비가 벽 뚫는 버그 수정
 2. 소환단계에서 좀비가 공중에 떠 있는 버그 수정
 3. 유니티 상에선 괜찮으나 빌드시 좀비 마주치면 화면만 프리징 되는 버그 수정
@@ -131,6 +129,63 @@
 1. UI추가(미션머신, 탈출구, Start Tip)
   1.1. 미션머신 하단에 동그란 모양의 비콘이미지를 설치했으나, 지속적으로 깜빡거리는 증상 발생, 금일 새벽 ~ 명일 픽스 예정
 2. 메인타이틀 화면 단순 이미지로 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -143,62 +198,39 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-1. 아이템 효과 구현
-2. 퍼즐 요소 추가(미션)
-+ UI 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 미완. 명일로 연장
-5. 완료
-6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 메인타이틀 UI 구현
-2. 테스트 및 게임 밸런스 조정
-3. 코드 리팩토링</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 미완
-3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
+    <x:t>1. 스테이지 맵 모델링
+2. 플레이어 / 몬스터 에셋 적용
+3. 플레이어 / 몬스터 애니메이션 적용
+4. 플레이어 / 몬스터 구현사항 프리팹화
+5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
+6. 밤하늘 Material 적용
+7. 탈출구 위치 알림용 경광등 구현</x:t>
   </x:si>
   <x:si>
     <x:t>구현
 1. 빌드 후 게임 실행시 특정 구간에서 화면 프리징 발생
   1.1. 특정 위치를 벗어나면 다시 움직임, 게임은 계속 진행되며 화면만 멈춤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타
+1.신규 레포지토리 개설, 기획안 하단 링크 첨부
+구현
+1. AI 좀비의 방향은 랜덤(Random.Range)로 구현.
+  1.1. 테스트 결과 간혹 대체적으로 한쪽 방향으로 좀비가 쏠리는 방향이 발생.
+  1.2. 아직은 더 효과적인 방법을 모르겠음.</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
@@ -210,40 +242,10 @@
 7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
   </x:si>
   <x:si>
-    <x:t>기타
-1. 2022.08.18 발생했던 Git 오류 지속.
-  1.1. 지도교수께서 직접 설정해 주셨으나 문제 지속
-  1.2. 더 이상 시간을 지체할 수 없어 신규 레포지토리 개설토록 함
-기획
-1. UI 및 게임 내 시스템 구현일정에 딜레이가 생겨 퍼즐요소 추가여부가 불가피함
-  1.1. 퍼즐요소는 배제 후 최대한 게임 시스템 구성에 집중
-  1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 버그픽스
-2. 코드 리팩토링
-3. 게임 밸런스 조정</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 완료
-2. 미완, 명일로 연장
-+  전일 4번 완료</x:t>
+2. 진행중
+3. 미완
+++ 게임매니저/씬메니저 구현 및 씬 변경 구현 완료</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1001,207 +1003,210 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:4" ht="49.149999999999999">
       <x:c r="B11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:4" ht="81.849999999999994">
       <x:c r="B12" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:4" ht="65.5">
       <x:c r="B13" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:4" ht="147.34999999999999">
       <x:c r="B14" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="2:4" ht="261.94999999999999">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="2:4" ht="81.849999999999994">
       <x:c r="B15" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="2:3" ht="49.149999999999999">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="2:4" ht="163.69999999999999">
       <x:c r="B16" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:2">
       <x:c r="B17" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="2:2">
       <x:c r="B20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="2:3" ht="49.149999999999999">
       <x:c r="B21" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="2:3">
       <x:c r="B22" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="2"/>
     </x:row>
     <x:row r="23" spans="2:3">
       <x:c r="B23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="2"/>
     </x:row>
     <x:row r="24" spans="2:3" ht="147.34999999999999">
       <x:c r="B24" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C24" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="2:2">
       <x:c r="B25" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="2:2">
       <x:c r="B26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="2:2">
       <x:c r="B27" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="2:3" ht="147.34999999999999">
       <x:c r="B28" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="2:3" ht="114.59999999999999">
       <x:c r="B29" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="2:3" ht="49.149999999999999">
       <x:c r="B30" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C30" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="2:2">
       <x:c r="B31" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="2:2">
       <x:c r="B32" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -19,55 +19,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
-  <x:si>
-    <x:t>1. 메인타이틀 UI 구현
-2. 테스트 및 게임 밸런스 조정
-3. 코드 리팩토링</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 미완, 명일로 연장
-+  전일 4번 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 버그픽스
-2. 코드 리팩토링
-3. 게임 밸런스 조정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 미완. 명일로 연장
-5. 완료
-6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-1. 아이템 효과 구현
-2. 퍼즐 요소 추가(미션)
-+ UI 구현</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
+  <x:si>
+    <x:t>VR 적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 인게임 UI 마무리 - 체력바, 배터리 게이지 변경예정
+2. HeartRate UI 추가
+3. 미션진행 UI 추가(게이지
+4. 게임오버 UI 및 리셋기능 구현
+5. 메인타이틀 UI 설계</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
@@ -80,21 +44,53 @@
 + 아이템 '배터리' 추가 - 배터리 게이지 40 회복 아이템</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 인게임 UI 마무리 - 체력바, 배터리 게이지 변경예정
-2. HeartRate UI 추가
-3. 미션진행 UI 추가(게이지
-4. 게임오버 UI 및 리셋기능 구현
-5. 메인타이틀 UI 설계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 미완
-3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
   </x:si>
   <x:si>
     <x:t>1. 미완
@@ -102,13 +98,6 @@
 3. 완료
 +  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
 +  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -131,43 +120,52 @@
 2. 메인타이틀 화면 단순 이미지로 전환</x:t>
   </x:si>
   <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 아이템 효과 방식 변경
+2. 좀비 종류별 개성 부여(이동속도/방향전환 주기 등)
+3. 테스트 / 버그픽스
+4. 코드 리팩토링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.09.02(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완
+3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 진행중
+3. 미완
+++ 게임매니저/씬메니저 구현 및 씬 변경 구현 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
   </x:si>
   <x:si>
     <x:t>구분</x:t>
@@ -176,16 +174,10 @@
     <x:t>예정</x:t>
   </x:si>
   <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 아이템 효과 구현
+2. 퍼즐 요소 추가(미션)
++ UI 구현</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -198,6 +190,16 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
+    <x:t>1. 메인타이틀 UI 구현
+2. 테스트 및 게임 밸런스 조정
+3. 코드 리팩토링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구현
+1. 빌드 후 게임 실행시 특정 구간에서 화면 프리징 발생
+  1.1. 특정 위치를 벗어나면 다시 움직임, 게임은 계속 진행되며 화면만 멈춤</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 스테이지 맵 모델링
 2. 플레이어 / 몬스터 에셋 적용
 3. 플레이어 / 몬스터 애니메이션 적용
@@ -207,32 +209,6 @@
 7. 탈출구 위치 알림용 경광등 구현</x:t>
   </x:si>
   <x:si>
-    <x:t>구현
-1. 빌드 후 게임 실행시 특정 구간에서 화면 프리징 발생
-  1.1. 특정 위치를 벗어나면 다시 움직임, 게임은 계속 진행되며 화면만 멈춤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기타
-1.신규 레포지토리 개설, 기획안 하단 링크 첨부
-구현
-1. AI 좀비의 방향은 랜덤(Random.Range)로 구현.
-  1.1. 테스트 결과 간혹 대체적으로 한쪽 방향으로 좀비가 쏠리는 방향이 발생.
-  1.2. 아직은 더 효과적인 방법을 모르겠음.</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 완료
 2. 완료
 3. 완료
@@ -243,9 +219,67 @@
   </x:si>
   <x:si>
     <x:t>1. 완료
-2. 진행중
-3. 미완
-++ 게임매니저/씬메니저 구현 및 씬 변경 구현 완료</x:t>
+2. 완료
+3. 완료
+4. 미완. 명일로 연장
+5. 완료
+6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완, 명일로 연장
++  전일 4번 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 버그픽스
+2. 코드 리팩토링
+3. 게임 밸런스 조정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타
+1.신규 레포지토리 개설, 기획안 하단 링크 첨부
+구현
+1. AI 좀비의 방향은 랜덤(Random.Range)로 구현.
+  1.1. 테스트 결과 간혹 대체적으로 한쪽 방향으로 좀비가 쏠리는 방향이 발생.
+  1.2. 아직은 더 효과적인 방법을 모르겠음.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.31(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.09.01(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.30(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.29(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.27(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.28(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 버그픽스
+2. 코드 리팩토링</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -990,7 +1024,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="B6:D32"/>
+  <x:dimension ref="B6:D45"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="2" max="2" width="24.5" style="1" customWidth="1"/>
@@ -1003,210 +1037,284 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="s">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="2:4" ht="49.149999999999999">
       <x:c r="B11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:4" ht="81.849999999999994">
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:4" ht="65.5">
       <x:c r="B13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:4" ht="147.34999999999999">
       <x:c r="B14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:4" ht="81.849999999999994">
       <x:c r="B15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:4" ht="163.69999999999999">
       <x:c r="B16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="2:3" ht="65.5">
+      <x:c r="B17" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C17" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="2:3" ht="32.75">
+      <x:c r="B18" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C18" s="2" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="2:3" customFormat="1" ht="32.75">
+      <x:c r="B19" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C19" s="2" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="2:3" customFormat="1">
+      <x:c r="B20" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C20" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="2:2" customFormat="1">
+      <x:c r="B21" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="2:2" customFormat="1">
+      <x:c r="B22" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="2:2" customFormat="1">
+      <x:c r="B23" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="2:2" customFormat="1">
+      <x:c r="B24" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" customFormat="1"/>
+    <x:row r="26" customFormat="1"/>
+    <x:row r="28" spans="2:2">
+      <x:c r="B28" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="2:3" ht="49.149999999999999">
+      <x:c r="B29" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C29" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="2:3">
+      <x:c r="B30" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C30" s="2"/>
+    </x:row>
+    <x:row r="31" spans="2:3">
+      <x:c r="B31" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C31" s="2"/>
+    </x:row>
+    <x:row r="32" spans="2:3" ht="147.34999999999999">
+      <x:c r="B32" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C32" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="2:2">
+      <x:c r="B33" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="2:2">
+      <x:c r="B34" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="2:2">
+      <x:c r="B35" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="2:3" ht="147.34999999999999">
+      <x:c r="B36" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C36" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="2:3" ht="114.59999999999999">
+      <x:c r="B37" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="2:2">
-      <x:c r="B17" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="2:2">
-      <x:c r="B20" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="2:3" ht="49.149999999999999">
-      <x:c r="B21" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C21" s="2" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="2:3">
-      <x:c r="B22" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C22" s="2"/>
-    </x:row>
-    <x:row r="23" spans="2:3">
-      <x:c r="B23" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C23" s="2"/>
-    </x:row>
-    <x:row r="24" spans="2:3" ht="147.34999999999999">
-      <x:c r="B24" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C24" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="2:2">
-      <x:c r="B25" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="2:2">
-      <x:c r="B26" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="2:2">
-      <x:c r="B27" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="2:3" ht="147.34999999999999">
-      <x:c r="B28" s="1" t="s">
+      <x:c r="C37" s="2" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="2:3" ht="49.149999999999999">
+      <x:c r="B38" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C28" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="2:3" ht="114.59999999999999">
-      <x:c r="B29" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C29" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="2:3" ht="49.149999999999999">
-      <x:c r="B30" s="1" t="s">
+      <x:c r="C38" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="2:2">
+      <x:c r="B39" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="2:2">
+      <x:c r="B40" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="2:2">
+      <x:c r="B41" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="2:2">
+      <x:c r="B42" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="2:2">
+      <x:c r="B43" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="2:2">
+      <x:c r="B44" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="2:2">
+      <x:c r="B45" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="C30" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="2:2">
-      <x:c r="B31" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="2:2">
-      <x:c r="B32" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -19,12 +19,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
-  <x:si>
-    <x:t>VR 적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+  <x:si>
+    <x:t>1. 메인타이틀 UI 구현
+2. 테스트 및 게임 밸런스 조정
+3. 코드 리팩토링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 미완. 명일로 연장
+5. 완료
+6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 미완
+2, 완료
+3. 완료
++  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
++  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
   </x:si>
   <x:si>
     <x:t>1. 인게임 UI 마무리 - 체력바, 배터리 게이지 변경예정
@@ -44,60 +58,41 @@
 + 아이템 '배터리' 추가 - 배터리 게이지 40 회복 아이템</x:t>
   </x:si>
   <x:si>
+    <x:t>1. 스테이지 맵 모델링
+2. 플레이어 / 몬스터 에셋 적용
+3. 플레이어 / 몬스터 애니메이션 적용
+4. 플레이어 / 몬스터 구현사항 프리팹화
+5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
+6. 밤하늘 Material 적용
+7. 탈출구 위치 알림용 경광등 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구현
+1. 빌드 후 게임 실행시 특정 구간에서 화면 프리징 발생
+  1.1. 특정 위치를 벗어나면 다시 움직임, 게임은 계속 진행되며 화면만 멈춤</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 미완
-2, 완료
-3. 완료
-+  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
-+  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 진행중
+3. 미완
+++ 게임매니저/씬메니저 구현 및 씬 변경 구현 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bug Fix:
+1. 케릭터, 좀비가 벽 뚫는 버그 수정
+2. 소환단계에서 좀비가 공중에 떠 있는 버그 수정
+3. 유니티 상에선 괜찮으나 빌드시 좀비 마주치면 화면만 프리징 되는 버그 수정
+Feat:
+1. UI추가(미션머신, 탈출구, Start Tip)
+  1.1. 미션머신 하단에 동그란 모양의 비콘이미지를 설치했으나, 지속적으로 깜빡거리는 증상 발생, 금일 새벽 ~ 명일 픽스 예정
+2. 메인타이틀 화면 단순 이미지로 전환</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -110,23 +105,9 @@
   1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
   </x:si>
   <x:si>
-    <x:t>Bug Fix:
-1. 케릭터, 좀비가 벽 뚫는 버그 수정
-2. 소환단계에서 좀비가 공중에 떠 있는 버그 수정
-3. 유니티 상에선 괜찮으나 빌드시 좀비 마주치면 화면만 프리징 되는 버그 수정
-Feat:
-1. UI추가(미션머신, 탈출구, Start Tip)
-  1.1. 미션머신 하단에 동그란 모양의 비콘이미지를 설치했으나, 지속적으로 깜빡거리는 증상 발생, 금일 새벽 ~ 명일 픽스 예정
-2. 메인타이틀 화면 단순 이미지로 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
   </x:si>
   <x:si>
     <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
@@ -139,45 +120,110 @@
 4. 코드 리팩토링</x:t>
   </x:si>
   <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 버그픽스
+2. 코드 리팩토링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
     <x:t>2022.09.02(금)</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 완료
-2. 미완
-3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 진행중
-3. 미완
-++ 게임매니저/씬메니저 구현 및 씬 변경 구현 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.31(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.29(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.30(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.27(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.09.01(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.28(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 진행중
+2. 진행중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VR 적용</x:t>
   </x:si>
   <x:si>
     <x:t>**지도교수님 피드백 후 마저 진행
 1. 아이템 효과 구현
 2. 퍼즐 요소 추가(미션)
 + UI 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 완료
+5. 완료
+6. 완료
+7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -190,50 +236,20 @@
     1.2.2. 처리 완료시까지 Commit 불가능</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 메인타이틀 UI 구현
-2. 테스트 및 게임 밸런스 조정
-3. 코드 리팩토링</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구현
-1. 빌드 후 게임 실행시 특정 구간에서 화면 프리징 발생
-  1.1. 특정 위치를 벗어나면 다시 움직임, 게임은 계속 진행되며 화면만 멈춤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 스테이지 맵 모델링
-2. 플레이어 / 몬스터 에셋 적용
-3. 플레이어 / 몬스터 애니메이션 적용
-4. 플레이어 / 몬스터 구현사항 프리팹화
-5. 플레이어 더미(마네킹) 구현(몬스터 감지범위 안쪽에 있을때 공격 받는 용도)
-6. 밤하늘 Material 적용
-7. 탈출구 위치 알림용 경광등 구현</x:t>
-  </x:si>
-  <x:si>
     <x:t>1. 완료
-2. 완료
-3. 완료
-4. 완료
-5. 완료
-6. 완료
-7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 미완. 명일로 연장
-5. 완료
-6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 미완, 명일로 연장
-+  전일 4번 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 버그픽스
-2. 코드 리팩토링
-3. 게임 밸런스 조정</x:t>
+2. 미완
+3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
   </x:si>
   <x:si>
     <x:t>기타
@@ -244,42 +260,36 @@
   1.2. 아직은 더 효과적인 방법을 모르겠음.</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.31(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.09.01(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.30(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.29(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.27(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.28(일)</x:t>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완, 명일로 연장
++  전일 4번 완료</x:t>
   </x:si>
   <x:si>
     <x:t>1. 버그픽스
-2. 코드 리팩토링</x:t>
+2. 코드 리팩토링
+3. 게임 밸런스 조정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완
+3. 테스트 진행중
+4. 진행중</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -347,7 +357,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -1027,294 +1040,303 @@
   <x:dimension ref="B6:D45"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.399999999999999"/>
   <x:cols>
-    <x:col min="2" max="2" width="24.5" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="80.125" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="90.625" style="1" customWidth="1"/>
-    <x:col min="6" max="6" width="26.75" style="1" customWidth="1"/>
-    <x:col min="7" max="7" width="67.625" style="1" customWidth="1"/>
-    <x:col min="8" max="8" width="58.25" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="24.5" style="2" customWidth="1"/>
+    <x:col min="3" max="3" width="80.125" style="2" customWidth="1"/>
+    <x:col min="4" max="4" width="90.625" style="2" customWidth="1"/>
+    <x:col min="6" max="6" width="26.75" style="2" customWidth="1"/>
+    <x:col min="7" max="7" width="67.625" style="2" customWidth="1"/>
+    <x:col min="8" max="8" width="58.25" style="2" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="6" spans="2:4">
-      <x:c r="B6" s="1" t="s">
+      <x:c r="B6" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="2:4" ht="131">
+      <x:c r="B7" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="2:4" ht="81.849999999999994">
+      <x:c r="B8" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="2:4" ht="114.59999999999999">
+      <x:c r="B9" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="s">
+    </x:row>
+    <x:row r="10" spans="2:4" ht="98.25">
+      <x:c r="B10" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="2:4" ht="49.149999999999999">
+      <x:c r="B11" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="2:4" ht="81.849999999999994">
+      <x:c r="B12" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="2:4" ht="65.5">
+      <x:c r="B13" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="2:4" ht="147.34999999999999">
+      <x:c r="B14" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="2:4" ht="81.849999999999994">
+      <x:c r="B15" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="2:4" ht="163.69999999999999">
+      <x:c r="B16" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D16" s="3" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="2:4" ht="65.5">
+      <x:c r="B17" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C17" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D17" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="2:4" ht="32.75">
+      <x:c r="B18" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D18" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="2:4" s="1" customFormat="1" ht="32.75">
+      <x:c r="B19" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C19" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D19" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="2:3" s="1" customFormat="1">
+      <x:c r="B20" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="2:2" s="1" customFormat="1">
+      <x:c r="B21" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="2:2" s="1" customFormat="1">
+      <x:c r="B22" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="s">
+    </x:row>
+    <x:row r="23" spans="2:2" s="1" customFormat="1">
+      <x:c r="B23" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="2:2" s="1" customFormat="1">
+      <x:c r="B24" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" s="1" customFormat="1"/>
+    <x:row r="26" s="1" customFormat="1"/>
+    <x:row r="28" spans="2:2">
+      <x:c r="B28" s="2" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="2:3" ht="49.149999999999999">
+      <x:c r="B29" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C29" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="2:3">
+      <x:c r="B30" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C30" s="3"/>
+    </x:row>
+    <x:row r="31" spans="2:3">
+      <x:c r="B31" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C31" s="3"/>
+    </x:row>
+    <x:row r="32" spans="2:3" ht="147.34999999999999">
+      <x:c r="B32" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C32" s="3" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="2:2">
+      <x:c r="B33" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="2:2">
+      <x:c r="B34" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="2:2">
+      <x:c r="B35" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="2:3" ht="147.34999999999999">
+      <x:c r="B36" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C36" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="2:3" ht="114.59999999999999">
+      <x:c r="B37" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C37" s="3" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="2:3" ht="49.149999999999999">
+      <x:c r="B38" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C38" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="2:2">
+      <x:c r="B39" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="2:4" ht="131">
-      <x:c r="B7" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="2:4" ht="81.849999999999994">
-      <x:c r="B8" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="2:4" ht="114.59999999999999">
-      <x:c r="B9" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D9" s="2" t="s">
+    <x:row r="40" spans="2:2">
+      <x:c r="B40" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="2:2">
+      <x:c r="B41" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="2:2">
+      <x:c r="B42" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="2:2">
+      <x:c r="B43" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="2:2">
+      <x:c r="B44" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="2:4" ht="98.25">
-      <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="2" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="2:4" ht="49.149999999999999">
-      <x:c r="B11" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="s">
+    <x:row r="45" spans="2:2">
+      <x:c r="B45" s="1" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="2:4" ht="81.849999999999994">
-      <x:c r="B12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="2:4" ht="65.5">
-      <x:c r="B13" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C13" s="2" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="2:4" ht="147.34999999999999">
-      <x:c r="B14" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C14" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="2:4" ht="81.849999999999994">
-      <x:c r="B15" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C15" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D15" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="2:4" ht="163.69999999999999">
-      <x:c r="B16" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C16" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D16" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="2:3" ht="65.5">
-      <x:c r="B17" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C17" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="2:3" ht="32.75">
-      <x:c r="B18" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C18" s="2" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="2:3" customFormat="1" ht="32.75">
-      <x:c r="B19" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C19" s="2" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="2:3" customFormat="1">
-      <x:c r="B20" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C20" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="2:2" customFormat="1">
-      <x:c r="B21" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="2:2" customFormat="1">
-      <x:c r="B22" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="2:2" customFormat="1">
-      <x:c r="B23" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="2:2" customFormat="1">
-      <x:c r="B24" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" customFormat="1"/>
-    <x:row r="26" customFormat="1"/>
-    <x:row r="28" spans="2:2">
-      <x:c r="B28" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="2:3" ht="49.149999999999999">
-      <x:c r="B29" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C29" s="2" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="2:3">
-      <x:c r="B30" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C30" s="2"/>
-    </x:row>
-    <x:row r="31" spans="2:3">
-      <x:c r="B31" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C31" s="2"/>
-    </x:row>
-    <x:row r="32" spans="2:3" ht="147.34999999999999">
-      <x:c r="B32" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C32" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="2:2">
-      <x:c r="B33" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="2:2">
-      <x:c r="B34" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="2:2">
-      <x:c r="B35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="2:3" ht="147.34999999999999">
-      <x:c r="B36" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C36" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="2:3" ht="114.59999999999999">
-      <x:c r="B37" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C37" s="2" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="2:3" ht="49.149999999999999">
-      <x:c r="B38" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C38" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="2:2">
-      <x:c r="B39" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="2:2">
-      <x:c r="B40" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="2:2">
-      <x:c r="B41" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="2:2">
-      <x:c r="B42" t="s">
-        <x:v>46</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="2:2">
-      <x:c r="B43" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="2:2">
-      <x:c r="B44" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="2:2">
-      <x:c r="B45" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
+++ b/_posts/Unity/UnityExample/프로젝트 완료,예정사항 표.xlsx
@@ -19,11 +19,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
-  <x:si>
-    <x:t>1. 메인타이틀 UI 구현
-2. 테스트 및 게임 밸런스 조정
-3. 코드 리팩토링</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="58">
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 1인칭 시점 카메라 세팅
+  1.2. 마우스로 시점/회전 구현
+  1.3. 전후좌우 이동 구현
+  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
+  1.5 뛰기/걷기 구현
+  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
@@ -34,11 +38,26 @@
 6. 완료</x:t>
   </x:si>
   <x:si>
-    <x:t>1. 미완
-2, 완료
-3. 완료
-+  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
-+  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
+    <x:t>1. 몬스터 구현
+  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
+  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
+  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
+  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구현 
+1. VR 적용해봤으나 타 PC 및 오큘러스에서 화면의 비정상적인 출력 확인
+  1.1. 담당교수님 판단 결과 렌더링 파이프라인 관련 설정해볼것을 권유</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타
+1. 2022.08.18 발생했던 Git 오류 지속.
+  1.1. 지도교수께서 직접 설정해 주셨으나 문제 지속
+  1.2. 더 이상 시간을 지체할 수 없어 신규 레포지토리 개설토록 함
+기획
+1. UI 및 게임 내 시스템 구현일정에 딜레이가 생겨 퍼즐요소 추가여부가 불가피함
+  1.1. 퍼즐요소는 배제 후 최대한 게임 시스템 구성에 집중
+  1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
   </x:si>
   <x:si>
     <x:t>1. 인게임 UI 마무리 - 체력바, 배터리 게이지 변경예정
@@ -46,6 +65,12 @@
 3. 미션진행 UI 추가(게이지
 4. 게임오버 UI 및 리셋기능 구현
 5. 메인타이틀 UI 설계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구현
+1. 렌더링 파이프라인 관련 설정해봤지만 증상 동일.
+1.1. 기간상 더 이상 시도할 수 있는 시간이 없어 3D버전으로만 마무리.
+1.2. 금일 테스트 후 주말간 마무리 버그픽스 예정</x:t>
   </x:si>
   <x:si>
     <x:t>1. 완료
@@ -58,6 +83,186 @@
 + 아이템 '배터리' 추가 - 배터리 게이지 40 회복 아이템</x:t>
   </x:si>
   <x:si>
+    <x:t>기타
+1.신규 레포지토리 개설, 기획안 하단 링크 첨부
+구현
+1. AI 좀비의 방향은 랜덤(Random.Range)로 구현.
+  1.1. 테스트 결과 간혹 대체적으로 한쪽 방향으로 좀비가 쏠리는 방향이 발생.
+  1.2. 아직은 더 효과적인 방법을 모르겠음.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
+2. 플레이어 체력에 따른 영상효과(흑백처리)
+3. 플레이어 체력 소진시 죽음 처리(조작불가)
+4. 맵 내 건물 / 미션장소 (구조물)설치
+5. 구조물 주변에서 일정 시간마다 아이템 드랍
+6. 사운드 추가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
+2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 아이템 효과 방식 변경
+2. 좀비 종류별 개성 부여(이동속도/방향전환 주기 등)
+3. 테스트 / 버그픽스
+4. 코드 리팩토링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료
+  1.5. 완료
+  1.6. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.09.01(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.30(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.29(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.27(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 진행중
+2. 진행중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.28(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.21(일)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.19(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.16(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.18(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.09.02(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.26(금)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.22(월)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.25(목)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.20(토)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.31(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.24(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.23(화)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2022.08.17(수)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
+2. 탈출구 조건 만족시 게이트 오픈 구현
+3. 체력에 따른 영상효과(흑백처리)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>**지도교수님 피드백 후 마저 진행
+1. 아이템 효과 구현
+2. 퍼즐 요소 추가(미션)
++ UI 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진행</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 미진행
+2. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 몬스터 구현
+  1.1. 완료
+  1.2. 완료
+  1.3. 완료
+  1.4. 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 진행중
+3. 미완
+++ 게임매니저/씬메니저 구현 및 씬 변경 구현 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. VR이식
+2. 테스트 및 QA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 버그픽스
+2. 코드 리팩토링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구현
+2. 기획
+3. 기타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구현
+1. 빌드 후 게임 실행시 특정 구간에서 화면 프리징 발생
+  1.1. 특정 위치를 벗어나면 다시 움직임, 게임은 계속 진행되며 화면만 멈춤</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 진행중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기타
+1. 사용하려고 했던 구조물 에셋의 개별 파일당 용량 초과(100MB이내 제한)로 Git push 에러 발생
+  1.1. (오후)지도교수님께 문의 결과 Git lfs 설치 권장.
+    1.1.1. 용량 초과하는 파일에 대해 쪼개서 push하는 방식
+    1.1.2. 추후 다운로드 시 pull을 통해 받아야 온전한 파일로 다운받을 수 있음
+  1.2. 검색 후 적용하려 했으나, 실패.
+    1.2.1. 명일 다시 여쭤보고 처리할 예정.
+    1.2.2. 처리 완료시까지 Commit 불가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 메인타이틀 UI 구현
+2. 테스트 및 게임 밸런스 조정
+3. 코드 리팩토링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 완료
+3. 완료
+4. 완료
+5. 완료
+6. 완료
+7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완
+3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
+  </x:si>
+  <x:si>
     <x:t>1. 스테이지 맵 모델링
 2. 플레이어 / 몬스터 에셋 적용
 3. 플레이어 / 몬스터 애니메이션 적용
@@ -67,22 +272,10 @@
 7. 탈출구 위치 알림용 경광등 구현</x:t>
   </x:si>
   <x:si>
-    <x:t>구현
-1. 빌드 후 게임 실행시 특정 구간에서 화면 프리징 발생
-  1.1. 특정 위치를 벗어나면 다시 움직임, 게임은 계속 진행되며 화면만 멈춤</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 진행중
-3. 미완
-++ 게임매니저/씬메니저 구현 및 씬 변경 구현 완료</x:t>
+    <x:t>일자별 예정/진행도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일자별 이슈</x:t>
   </x:si>
   <x:si>
     <x:t>Bug Fix:
@@ -95,190 +288,7 @@
 2. 메인타이틀 화면 단순 이미지로 전환</x:t>
   </x:si>
   <x:si>
-    <x:t>기타
-1. 2022.08.18 발생했던 Git 오류 지속.
-  1.1. 지도교수께서 직접 설정해 주셨으나 문제 지속
-  1.2. 더 이상 시간을 지체할 수 없어 신규 레포지토리 개설토록 함
-기획
-1. UI 및 게임 내 시스템 구현일정에 딜레이가 생겨 퍼즐요소 추가여부가 불가피함
-  1.1. 퍼즐요소는 배제 후 최대한 게임 시스템 구성에 집중
-  1.2. 게임 시스템 구현 및 안정시 여유 일정에 따라 퍼즐 추가예정.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 씬 전환 기능 추가(타이틀 - 인게임)
-2. 탈출구 조건 만족시 게이트 오픈 구현
-3. 체력에 따른 영상효과(흑백처리)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 맵 내 건물 / 미션장소 / 구조물 설치
-2. UI추가(타이틀, 인게임, GameOver, Stage Clear, Pause)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 아이템 효과 방식 변경
-2. 좀비 종류별 개성 부여(이동속도/방향전환 주기 등)
-3. 테스트 / 버그픽스
-4. 코드 리팩토링</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>진행</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 1인칭 시점 카메라 세팅
-  1.2. 마우스로 시점/회전 구현
-  1.3. 전후좌우 이동 구현
-  1.4. 손전등 구현(손전등 켠 상태에서 배터리 소모)
-  1.5 뛰기/걷기 구현
-  1.6. 가장 가까운 적과의 거리를 바탕으로 두려움 수치 구현(거리에 따라 심박소리 속도를 다르게 하기 위함)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 버그픽스
-2. 코드 리팩토링</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구현
-2. 기획
-3. 기타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.18(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.09.02(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.26(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.22(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.17(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.19(금)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.21(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.20(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.25(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.16(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.31(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.24(수)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.23(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.29(월)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.30(화)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.27(토)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.09.01(목)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2022.08.28(일)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 진행중
-2. 진행중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 이슈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VR 적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>**지도교수님 피드백 후 마저 진행
-1. 아이템 효과 구현
-2. 퍼즐 요소 추가(미션)
-+ UI 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 완료
-3. 완료
-4. 완료
-5. 완료
-6. 완료
-7. 완료 - 프로토 타입, 추후 디테일 수정 예정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기타
-1. 사용하려고 했던 구조물 에셋의 개별 파일당 용량 초과(100MB이내 제한)로 Git push 에러 발생
-  1.1. (오후)지도교수님께 문의 결과 Git lfs 설치 권장.
-    1.1.1. 용량 초과하는 파일에 대해 쪼개서 push하는 방식
-    1.1.2. 추후 다운로드 시 pull을 통해 받아야 온전한 파일로 다운받을 수 있음
-  1.2. 검색 후 적용하려 했으나, 실패.
-    1.2.1. 명일 다시 여쭤보고 처리할 예정.
-    1.2.2. 처리 완료시까지 Commit 불가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 미완
-3. 인벤토리 UI 및 기능구현 완료. CSV로 아이템 추가 가능하도록 설계함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일자별 예정/진행도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 공격 및 공격판정(전일 애니메이션만 적용 완료)
-2. 플레이어 체력에 따른 영상효과(흑백처리)
-3. 플레이어 체력 소진시 죽음 처리(조작불가)
-4. 맵 내 건물 / 미션장소 (구조물)설치
-5. 구조물 주변에서 일정 시간마다 아이템 드랍
-6. 사운드 추가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기타
-1.신규 레포지토리 개설, 기획안 하단 링크 첨부
-구현
-1. AI 좀비의 방향은 랜덤(Random.Range)로 구현.
-  1.1. 테스트 결과 간혹 대체적으로 한쪽 방향으로 좀비가 쏠리는 방향이 발생.
-  1.2. 아직은 더 효과적인 방법을 모르겠음.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 몬스터 구현
-  1.1. 몬스터의 ‘시야’에 들어오면 플레이어 뛰어서 추적
-  1.2. 시야에 들어오지 않았더라도 범위 내 플레이어가 뛰는 상태로 이동시 추적
-  1.3. 플레이어 추적 중 일정 거리 이상 멀어지면 평시 상태로 돌아옴
-  1.4. 타겟이 감지되지 않았을 때는 랜덤한 방향으로 이동, 4초마다 한번씩 랜덤으로 방향 전환</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 테스트 오브젝트로 플레이어 스크립트 구현
-  1.1. 완료
-  1.2. 완료
-  1.3. 완료
-  1.4. 완료
-  1.5. 완료
-  1.6. 완료</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 완료
-2. 미완, 명일로 연장
-+  전일 4번 완료</x:t>
+    <x:t>1. VR 이식</x:t>
   </x:si>
   <x:si>
     <x:t>1. 버그픽스
@@ -290,6 +300,18 @@
 2. 미완
 3. 테스트 진행중
 4. 진행중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 완료
+2. 미완, 명일로 연장
++  전일 4번 완료</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 미완
+2, 완료
+3. 완료
++  게임 시작시 미션 구조물, 아이템 스폰 위치 랜덤설정, 아이템은 습득시 일정시간 후 랜덤위치 생성
++  게임 시작시 몬스터 스폰 위치 랜덤설정, 미션 진행도에 따라 추가 소환</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1050,54 +1072,54 @@
   <x:sheetData>
     <x:row r="6" spans="2:4">
       <x:c r="B6" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="2:4" ht="131">
       <x:c r="B7" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="2:4" ht="81.849999999999994">
       <x:c r="B8" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D8" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:4" ht="114.59999999999999">
       <x:c r="B9" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D9" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="2:4" ht="98.25">
       <x:c r="B10" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D10" s="3" t="s">
         <x:v>1</x:v>
@@ -1108,166 +1130,193 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D11" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="2:4" ht="81.849999999999994">
       <x:c r="B12" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D12" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="2:4" ht="65.5">
       <x:c r="B13" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="2:4" ht="147.34999999999999">
       <x:c r="B14" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="2:4" ht="81.849999999999994">
       <x:c r="B15" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="2:4" ht="163.69999999999999">
       <x:c r="B16" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D16" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="2:4" ht="65.5">
       <x:c r="B17" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D17" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="2:4" ht="32.75">
       <x:c r="B18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D18" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="2:4" s="1" customFormat="1" ht="32.75">
       <x:c r="B19" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C19" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D19" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="2:4" s="1" customFormat="1" ht="32.75">
+      <x:c r="B20" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C20" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D20" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="2:4" s="1" customFormat="1">
+      <x:c r="B21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D21" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="2:4" s="1" customFormat="1">
+      <x:c r="B22" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C22" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D22" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="2:4" s="1" customFormat="1">
+      <x:c r="B23" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C23" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D23" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="2:4" s="1" customFormat="1" ht="32.75">
+      <x:c r="B24" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C24" s="3" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D24" s="3" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="C19" s="3" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D19" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="2:3" s="1" customFormat="1">
-      <x:c r="B20" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="2:2" s="1" customFormat="1">
-      <x:c r="B21" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="2:2" s="1" customFormat="1">
-      <x:c r="B22" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="2:2" s="1" customFormat="1">
-      <x:c r="B23" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="2:2" s="1" customFormat="1">
-      <x:c r="B24" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" s="1" customFormat="1"/>
     <x:row r="26" s="1" customFormat="1"/>
     <x:row r="28" spans="2:2">
       <x:c r="B28" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="2:3" ht="49.149999999999999">
       <x:c r="B29" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C29" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="2:3">
       <x:c r="B30" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C30" s="3"/>
     </x:row>
     <x:row r="31" spans="2:3">
       <x:c r="B31" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C31" s="3"/>
     </x:row>
     <x:row r="32" spans="2:3" ht="147.34999999999999">
       <x:c r="B32" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="2:2">
       <x:c r="B33" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="2:2">
@@ -1277,66 +1326,73 @@
     </x:row>
     <x:row r="35" spans="2:2">
       <x:c r="B35" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="2:3" ht="147.34999999999999">
       <x:c r="B36" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="2:3" ht="114.59999999999999">
       <x:c r="B37" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="2:3" ht="49.149999999999999">
       <x:c r="B38" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="2:2">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="2:3">
       <x:c r="B39" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C39" s="3"/>
     </x:row>
     <x:row r="40" spans="2:2">
       <x:c r="B40" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="2:2">
       <x:c r="B41" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="2:2">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="2:3" ht="49.149999999999999">
       <x:c r="B42" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C42" s="3" t="s">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="2:2">
       <x:c r="B43" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="2:2">
       <x:c r="B44" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="2:2">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="2:3" ht="65.5">
       <x:c r="B45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C45" s="3" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
